--- a/Planning_ST_Antoine_2-22nov.xlsx
+++ b/Planning_ST_Antoine_2-22nov.xlsx
@@ -28,6 +28,30 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="C24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cp (Solidarité)</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K14" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Indisponible</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="S9" authorId="0">
       <text>
         <r>
@@ -37,6 +61,30 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Congé</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S13" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Indisponible</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AA24" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Cp (Solidarité)</t>
         </r>
       </text>
     </comment>
@@ -1286,31 +1334,23 @@
         <v>14</v>
       </c>
       <c r="B11" s="13"/>
-      <c r="C11" s="14" t="n">
-        <v>0.486111111111111</v>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E11" s="15" t="n">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15" t="str">
         <f aca="false">IF(C11="","",D11-C11)</f>
-        <v>0.138888888888889</v>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="G11" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="H11" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15" t="str">
         <f aca="false">IF(F11="","",G11-F11)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="I11" s="16" t="n">
+        <v/>
+      </c>
+      <c r="I11" s="16" t="str">
         <f aca="false">IF(H11="",IF(E11="","",IF(E11&lt;$C$2,"# Matin 1",IF(E11&gt;$D$2,"# Matin 2",E11))
 ),IF(E11="",IF(H11&lt;$C$2,"# AprèsMidi 1",IF(H11&gt;$D$2,"# AprèsMidi 2",H11)
 ),IF(H11&gt;$D$2,"# AprèsMidi 2",IF(E11&gt;$D$2,"# Matin 2",IF((F11-D11)&gt;$B$2,"# Repas 1", IF((F11-D11)&lt;$A$2,"# Repas 2",IF((E11+H11)&lt;$E$2,"# Jour 1",IF((E11+H11)&gt;$F$2,"# Jour 2",E11+H11))))))))</f>
-        <v>0.291666666666667</v>
+        <v/>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="14" t="n">
@@ -1339,23 +1379,31 @@
 ),IF(P11&gt;$D$2,"# AprèsMidi 2",IF(M11&gt;$D$2,"# Matin 2",IF((N11-L11)&gt;$B$2,"# Repas 1", IF((N11-L11)&lt;$A$2,"# Repas 2",IF((M11+P11)&lt;$E$2,"# Jour 1",IF((M11+P11)&gt;$F$2,"# Jour 2",M11+P11))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S11" s="14"/>
-      <c r="T11" s="14"/>
-      <c r="U11" s="15" t="str">
+      <c r="S11" s="14" t="n">
+        <v>0.517361111111111</v>
+      </c>
+      <c r="T11" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="U11" s="15" t="n">
         <f aca="false">IF(S11="","",T11-S11)</f>
-        <v/>
-      </c>
-      <c r="V11" s="14"/>
-      <c r="W11" s="14"/>
-      <c r="X11" s="15" t="str">
+        <v>0.107638888888889</v>
+      </c>
+      <c r="V11" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="W11" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="X11" s="15" t="n">
         <f aca="false">IF(V11="","",W11-V11)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="Y11" s="16" t="n">
         <f aca="false">IF(X11="",IF(U11="","",IF(U11&lt;$C$2,"# Matin 1",IF(U11&gt;$D$2,"# Matin 2",U11))
 ),IF(U11="",IF(X11&lt;$C$2,"# AprèsMidi 1",IF(X11&gt;$D$2,"# AprèsMidi 2",X11)
 ),IF(X11&gt;$D$2,"# AprèsMidi 2",IF(U11&gt;$D$2,"# Matin 2",IF((V11-T11)&gt;$B$2,"# Repas 1", IF((V11-T11)&lt;$A$2,"# Repas 2",IF((U11+X11)&lt;$E$2,"# Jour 1",IF((U11+X11)&gt;$F$2,"# Jour 2",U11+X11))))))))</f>
-        <v/>
+        <v>0.260416666666667</v>
       </c>
       <c r="AA11" s="14"/>
       <c r="AB11" s="14"/>
@@ -1484,23 +1532,31 @@
         <v>16</v>
       </c>
       <c r="B13" s="13"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="15" t="str">
+      <c r="C13" s="14" t="n">
+        <v>0.486111111111111</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E13" s="15" t="n">
         <f aca="false">IF(C13="","",D13-C13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15" t="str">
+        <v>0.138888888888889</v>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>0.666666666666667</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>0.819444444444444</v>
+      </c>
+      <c r="H13" s="15" t="n">
         <f aca="false">IF(F13="","",G13-F13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="16" t="str">
+        <v>0.152777777777778</v>
+      </c>
+      <c r="I13" s="16" t="n">
         <f aca="false">IF(H13="",IF(E13="","",IF(E13&lt;$C$2,"# Matin 1",IF(E13&gt;$D$2,"# Matin 2",E13))
 ),IF(E13="",IF(H13&lt;$C$2,"# AprèsMidi 1",IF(H13&gt;$D$2,"# AprèsMidi 2",H13)
 ),IF(H13&gt;$D$2,"# AprèsMidi 2",IF(E13&gt;$D$2,"# Matin 2",IF((F13-D13)&gt;$B$2,"# Repas 1", IF((F13-D13)&lt;$A$2,"# Repas 2",IF((E13+H13)&lt;$E$2,"# Jour 1",IF((E13+H13)&gt;$F$2,"# Jour 2",E13+H13))))))))</f>
-        <v/>
+        <v>0.291666666666667</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="14" t="n">
@@ -1529,31 +1585,23 @@
 ),IF(P13&gt;$D$2,"# AprèsMidi 2",IF(M13&gt;$D$2,"# Matin 2",IF((N13-L13)&gt;$B$2,"# Repas 1", IF((N13-L13)&lt;$A$2,"# Repas 2",IF((M13+P13)&lt;$E$2,"# Jour 1",IF((M13+P13)&gt;$F$2,"# Jour 2",M13+P13))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S13" s="14" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="T13" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="U13" s="15" t="n">
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="15" t="str">
         <f aca="false">IF(S13="","",T13-S13)</f>
-        <v>0.107638888888889</v>
-      </c>
-      <c r="V13" s="14" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="W13" s="14" t="n">
-        <v>0.819444444444444</v>
-      </c>
-      <c r="X13" s="15" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="14"/>
+      <c r="W13" s="14"/>
+      <c r="X13" s="15" t="str">
         <f aca="false">IF(V13="","",W13-V13)</f>
-        <v>0.152777777777778</v>
-      </c>
-      <c r="Y13" s="16" t="n">
+        <v/>
+      </c>
+      <c r="Y13" s="16" t="str">
         <f aca="false">IF(X13="",IF(U13="","",IF(U13&lt;$C$2,"# Matin 1",IF(U13&gt;$D$2,"# Matin 2",U13))
 ),IF(U13="",IF(X13&lt;$C$2,"# AprèsMidi 1",IF(X13&gt;$D$2,"# AprèsMidi 2",X13)
 ),IF(X13&gt;$D$2,"# AprèsMidi 2",IF(U13&gt;$D$2,"# Matin 2",IF((V13-T13)&gt;$B$2,"# Repas 1", IF((V13-T13)&lt;$A$2,"# Repas 2",IF((U13+X13)&lt;$E$2,"# Jour 1",IF((U13+X13)&gt;$F$2,"# Jour 2",U13+X13))))))))</f>
-        <v>0.260416666666667</v>
+        <v/>
       </c>
       <c r="AA13" s="14"/>
       <c r="AB13" s="14"/>
@@ -2251,24 +2299,24 @@
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="14" t="n">
-        <v>0.409722222222222</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="L24" s="14" t="n">
         <v>0.583333333333333</v>
       </c>
       <c r="M24" s="15" t="n">
         <f aca="false">IF(K24="","",L24-K24)</f>
-        <v>0.173611111111111</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="N24" s="14" t="n">
         <v>0.625</v>
       </c>
       <c r="O24" s="14" t="n">
-        <v>0.743055555555556</v>
+        <v>0.75</v>
       </c>
       <c r="P24" s="15" t="n">
         <f aca="false">IF(N24="","",O24-N24)</f>
-        <v>0.118055555555556</v>
+        <v>0.125</v>
       </c>
       <c r="Q24" s="16" t="n">
         <f aca="false">IF(P24="",IF(M24="","",IF(M24&lt;$C$2,"# Matin 1",IF(M24&gt;$D$2,"# Matin 2",M24))
@@ -2276,31 +2324,27 @@
 ),IF(P24&gt;$D$2,"# AprèsMidi 2",IF(M24&gt;$D$2,"# Matin 2",IF((N24-L24)&gt;$B$2,"# Repas 1", IF((N24-L24)&lt;$A$2,"# Repas 2",IF((M24+P24)&lt;$E$2,"# Jour 1",IF((M24+P24)&gt;$F$2,"# Jour 2",M24+P24))))))))</f>
         <v>0.291666666666667</v>
       </c>
-      <c r="S24" s="14" t="n">
-        <v>0.517361111111111</v>
-      </c>
-      <c r="T24" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="U24" s="15" t="n">
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="15" t="str">
         <f aca="false">IF(S24="","",T24-S24)</f>
-        <v>0.107638888888889</v>
+        <v/>
       </c>
       <c r="V24" s="14" t="n">
-        <v>0.666666666666667</v>
+        <v>0.583333333333333</v>
       </c>
       <c r="W24" s="14" t="n">
-        <v>0.819444444444444</v>
+        <v>0.791666666666667</v>
       </c>
       <c r="X24" s="15" t="n">
         <f aca="false">IF(V24="","",W24-V24)</f>
-        <v>0.152777777777778</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="Y24" s="16" t="n">
         <f aca="false">IF(X24="",IF(U24="","",IF(U24&lt;$C$2,"# Matin 1",IF(U24&gt;$D$2,"# Matin 2",U24))
 ),IF(U24="",IF(X24&lt;$C$2,"# AprèsMidi 1",IF(X24&gt;$D$2,"# AprèsMidi 2",X24)
 ),IF(X24&gt;$D$2,"# AprèsMidi 2",IF(U24&gt;$D$2,"# Matin 2",IF((V24-T24)&gt;$B$2,"# Repas 1", IF((V24-T24)&lt;$A$2,"# Repas 2",IF((U24+X24)&lt;$E$2,"# Jour 1",IF((U24+X24)&gt;$F$2,"# Jour 2",U24+X24))))))))</f>
-        <v>0.260416666666667</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="AA24" s="14"/>
       <c r="AB24" s="14"/>
@@ -2747,7 +2791,7 @@
       <c r="X29" s="21"/>
       <c r="Y29" s="20" t="n">
         <f aca="false">SUM(Y22:Y28)</f>
-        <v>1.04166666666667</v>
+        <v>0.989583333333334</v>
       </c>
       <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
@@ -2794,7 +2838,7 @@
       <c r="X30" s="3"/>
       <c r="Y30" s="22" t="str">
         <f aca="false">+IF(OR((Y29&gt;$H$2),(Y29&lt;$G$2)),"# Semaine 1","Ok")</f>
-        <v>Ok</v>
+        <v># Semaine 1</v>
       </c>
       <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>

--- a/Planning_ST_Antoine_2-22nov.xlsx
+++ b/Planning_ST_Antoine_2-22nov.xlsx
@@ -28,18 +28,6 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C24" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Cp (Solidarité)</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="K14" authorId="0">
       <text>
         <r>
@@ -73,18 +61,6 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">Indisponible</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AA24" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Cp (Solidarité)</t>
         </r>
       </text>
     </comment>
@@ -2279,23 +2255,31 @@
         <v>14</v>
       </c>
       <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="15" t="str">
+      <c r="C24" s="14" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <v>0.583333333333333</v>
+      </c>
+      <c r="E24" s="15" t="n">
         <f aca="false">IF(C24="","",D24-C24)</f>
-        <v/>
-      </c>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="15" t="str">
+        <v>0.125</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <v>0.791666666666667</v>
+      </c>
+      <c r="H24" s="15" t="n">
         <f aca="false">IF(F24="","",G24-F24)</f>
-        <v/>
-      </c>
-      <c r="I24" s="16" t="str">
+        <v>0.166666666666667</v>
+      </c>
+      <c r="I24" s="16" t="n">
         <f aca="false">IF(H24="",IF(E24="","",IF(E24&lt;$C$2,"# Matin 1",IF(E24&gt;$D$2,"# Matin 2",E24))
 ),IF(E24="",IF(H24&lt;$C$2,"# AprèsMidi 1",IF(H24&gt;$D$2,"# AprèsMidi 2",H24)
 ),IF(H24&gt;$D$2,"# AprèsMidi 2",IF(E24&gt;$D$2,"# Matin 2",IF((F24-D24)&gt;$B$2,"# Repas 1", IF((F24-D24)&lt;$A$2,"# Repas 2",IF((E24+H24)&lt;$E$2,"# Jour 1",IF((E24+H24)&gt;$F$2,"# Jour 2",E24+H24))))))))</f>
-        <v/>
+        <v>0.291666666666667</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="14" t="n">
@@ -2465,31 +2449,23 @@
         <v>16</v>
       </c>
       <c r="B26" s="13"/>
-      <c r="C26" s="14" t="n">
-        <v>0.458333333333333</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>0.583333333333333</v>
-      </c>
-      <c r="E26" s="15" t="n">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15" t="str">
         <f aca="false">IF(C26="","",D26-C26)</f>
-        <v>0.125</v>
-      </c>
-      <c r="F26" s="14" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="G26" s="14" t="n">
-        <v>0.791666666666667</v>
-      </c>
-      <c r="H26" s="15" t="n">
+        <v/>
+      </c>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="15" t="str">
         <f aca="false">IF(F26="","",G26-F26)</f>
-        <v>0.166666666666667</v>
-      </c>
-      <c r="I26" s="16" t="n">
+        <v/>
+      </c>
+      <c r="I26" s="16" t="str">
         <f aca="false">IF(H26="",IF(E26="","",IF(E26&lt;$C$2,"# Matin 1",IF(E26&gt;$D$2,"# Matin 2",E26))
 ),IF(E26="",IF(H26&lt;$C$2,"# AprèsMidi 1",IF(H26&gt;$D$2,"# AprèsMidi 2",H26)
 ),IF(H26&gt;$D$2,"# AprèsMidi 2",IF(E26&gt;$D$2,"# Matin 2",IF((F26-D26)&gt;$B$2,"# Repas 1", IF((F26-D26)&lt;$A$2,"# Repas 2",IF((E26+H26)&lt;$E$2,"# Jour 1",IF((E26+H26)&gt;$F$2,"# Jour 2",E26+H26))))))))</f>
-        <v>0.291666666666667</v>
+        <v/>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="14" t="n">
